--- a/artfynd/A 30870-2024 artfynd.xlsx
+++ b/artfynd/A 30870-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>112089464</v>
       </c>
       <c r="B2" t="n">
-        <v>96771</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,14 +707,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rösåsen (Rösåsen), Dlr</t>
+          <t>Rösåsen, Rösåsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536919</v>
+        <v>536918</v>
       </c>
       <c r="R2" t="n">
-        <v>6701910</v>
+        <v>6701909</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,12 +776,7 @@
         <v>112089474</v>
       </c>
       <c r="B3" t="n">
-        <v>96771</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,11 +805,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rösåsen (Rösåsen), Dlr</t>
+          <t>Rösåsen, Rösåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536914</v>
+        <v>536913</v>
       </c>
       <c r="R3" t="n">
         <v>6701889</v>
@@ -884,12 +874,7 @@
         <v>112089500</v>
       </c>
       <c r="B4" t="n">
-        <v>96771</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,7 +903,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rösåsen (Rösåsen), Dlr</t>
+          <t>Rösåsen, Rösåsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">

--- a/artfynd/A 30870-2024 artfynd.xlsx
+++ b/artfynd/A 30870-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112089464</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112089474</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,8 +981,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112089500</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>